--- a/Retail Upload Log Portfolio Example.xlsx
+++ b/Retail Upload Log Portfolio Example.xlsx
@@ -285,7 +285,7 @@
     <t>I built this workflow from scratch to show how a flat query output becomes a functional intake and triage process. Starting from the raw upload log, I designed a tiered workbook that separates files into actionable categories, tracks vendor contact and escalation notes, and surfaces recurring issues like persistent format non-compliance. The Quick Stats tab provides running error totals at both the vendor and file level to reflect the users inputs in the workbook..</t>
   </si>
   <si>
-    <t>This workflow shows that worked and resolved are not the same thing. A file can be worked via vendor contacted, ticket created, sales team informed, have  other errors corrected for ingestion and still have errors remain outstanding. The Completed and Completed with Errors columns reflect that difference intentionally.</t>
+    <t>This workflow shows that worked and resolved are not the same thing, but both can stillbe accounted for. A file can be marked completed with errors when a vendor is contacted, ticket created, sales team informed, have other errors within the file are corrected for ingestion and yet still have errors that remain outstanding. The Completed and Completed with Errors columns reflect that difference intentionally.</t>
   </si>
   <si>
     <t>One vendor, Hexford Wholesale, submits exclusively in PDF format, which the system cannot process. They appear in Completed with Errors because contact was made, but their records remain uningested</t>
@@ -1597,7 +1597,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -1668,11 +1668,6 @@
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF6AA84F"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -1868,11 +1863,11 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6119,14 +6114,14 @@
     </pivotField>
     <pivotField name="Vendor Name" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
       <items>
-        <item x="0"/>
+        <item sd="0" x="0"/>
         <item x="1"/>
-        <item x="2"/>
+        <item sd="0" x="2"/>
         <item x="3"/>
         <item x="4"/>
         <item x="5"/>
         <item x="6"/>
-        <item x="7"/>
+        <item sd="0" x="7"/>
         <item x="8"/>
         <item x="9"/>
         <item x="10"/>
@@ -23998,15 +23993,15 @@
     <row r="20"/>
     <row r="21"/>
     <row r="22">
-      <c r="E22" s="27"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
       <c r="H22" s="30"/>
       <c r="I22" s="30"/>
     </row>
     <row r="23">
-      <c r="E23" s="42"/>
-      <c r="F23" s="43"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
       <c r="G23" s="35"/>
       <c r="H23" s="38"/>
       <c r="I23" s="38"/>
